--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdCommandReceive002.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdCommandReceive002.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2715" windowWidth="13020" windowHeight="4320"/>
@@ -50,10 +50,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>交易完成度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>币种</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -79,6 +75,10 @@
   </si>
   <si>
     <t>投标标位</t>
+  </si>
+  <si>
+    <t>交易完成度（%）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -194,7 +194,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -229,7 +229,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -460,7 +460,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -484,28 +484,28 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
         <v>13</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>14</v>
       </c>
       <c r="L1" t="s">
         <v>7</v>
       </c>
       <c r="M1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>10</v>
-      </c>
-      <c r="P1" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdCommandReceive002.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdCommandReceive002.xlsx
@@ -77,7 +77,7 @@
     <t>投标标位</t>
   </si>
   <si>
-    <t>交易完成度（%）</t>
+    <t>交易完成度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
